--- a/jarvis/accounting/facturare/assets/Anexa_Proforma_Template.xlsx
+++ b/jarvis/accounting/facturare/assets/Anexa_Proforma_Template.xlsx
@@ -1,159 +1,46 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10514"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sebastiansabo/Downloads/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{802336E6-6B46-D84C-9F9B-72F4A5FF626C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="880" windowWidth="36000" windowHeight="22500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
-  <si>
-    <t>Client</t>
-  </si>
-  <si>
-    <t>GENERAL LEASE NV</t>
-  </si>
-  <si>
-    <t>Client Address</t>
-  </si>
-  <si>
-    <t>Overhaamlaan 71, 3700 Tongeren, BELGIA</t>
-  </si>
-  <si>
-    <t>Client VAT</t>
-  </si>
-  <si>
-    <t>BE0431586751</t>
-  </si>
-  <si>
-    <t>Invoice Date</t>
-  </si>
-  <si>
-    <t>2026-04-29</t>
-  </si>
-  <si>
-    <t>Start No</t>
-  </si>
-  <si>
-    <t>Contract Ref</t>
-  </si>
-  <si>
-    <t>ctr 677/03.04.2026</t>
-  </si>
-  <si>
-    <t>Anexa Ref</t>
-  </si>
-  <si>
-    <t>Anexa 1 la CTR.677 din 03.04.2026</t>
-  </si>
-  <si>
-    <t>Nr. Comanda</t>
-  </si>
-  <si>
-    <t>Model</t>
-  </si>
-  <si>
-    <t>Color</t>
-  </si>
-  <si>
-    <t>VIN</t>
-  </si>
-  <si>
-    <t>Rest de plata</t>
-  </si>
-  <si>
-    <t>Audi Q5 40 TDI quattro</t>
-  </si>
-  <si>
-    <t>Gri Daytona perlat</t>
-  </si>
-  <si>
-    <t>WAUZZZGU8S2130154</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="#,##0\ &quot;€&quot;"/>
-  </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
+      <b val="1"/>
       <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="3">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD9D9D9"/>
-        <bgColor rgb="FFD9D9D9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4472C4"/>
-        <bgColor rgb="FF4472C4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor rgb="FFFFFF00"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="00D9E1F2"/>
+        <bgColor rgb="00D9E1F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -166,49 +53,94 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -496,105 +428,102 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="30" customWidth="1"/>
-    <col min="3" max="3" width="22" customWidth="1"/>
-    <col min="4" max="4" width="24" customWidth="1"/>
-    <col min="5" max="5" width="15" customWidth="1"/>
-    <col min="6" max="6" width="14" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="24.5" bestFit="1" customWidth="1"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Nr. Comanda</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Culoare</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>VIN</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Rest de plata</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Contract ref</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Anexa ref</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Invoice Date</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B5" s="2"/>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B6" s="2"/>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A7" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A8" s="4">
-        <v>150966</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E8" s="5">
-        <v>50547</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H8">
-        <v>1</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>7</v>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>12345</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Audi Q3 Sportback 35 TFSI</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Mythos Black</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>WAUZZZ8V...</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>CTR-001</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>ANX-001</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/jarvis/accounting/facturare/assets/Anexa_Proforma_Template.xlsx
+++ b/jarvis/accounting/facturare/assets/Anexa_Proforma_Template.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -487,6 +487,11 @@
           <t>Invoice Date</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Qty</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
@@ -524,6 +529,9 @@
         <is>
           <t>2026-04-30</t>
         </is>
+      </c>
+      <c r="I2" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
